--- a/docs/d/89/inyear.xlsx
+++ b/docs/d/89/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/89/inyear.xlsx
+++ b/docs/d/89/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1028,11 @@
       <c r="AB3" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC3" s="4" t="inlineStr"/>
+      <c r="AC3" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -3811,7 +3815,11 @@
       <c r="AB30" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC30" s="4" t="inlineStr"/>
+      <c r="AC30" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -5045,7 +5053,11 @@
       <c r="AB42" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC42" s="4" t="inlineStr"/>
+      <c r="AC42" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
@@ -5352,7 +5364,11 @@
       <c r="AB45" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC45" s="4" t="inlineStr"/>
+      <c r="AC45" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
@@ -5764,7 +5780,11 @@
       <c r="AB49" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC49" s="4" t="inlineStr"/>
+      <c r="AC49" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
@@ -6911,7 +6931,11 @@
       <c r="AB60" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC60" s="4" t="inlineStr"/>
+      <c r="AC60" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
@@ -7315,7 +7339,11 @@
       <c r="AB64" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC64" s="4" t="inlineStr"/>
+      <c r="AC64" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
@@ -8547,7 +8575,11 @@
       <c r="AB76" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC76" s="4" t="inlineStr"/>
+      <c r="AC76" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
@@ -9371,7 +9403,11 @@
       <c r="AB84" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC84" s="4" t="inlineStr"/>
+      <c r="AC84" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
@@ -10619,7 +10655,11 @@
       <c r="AB96" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC96" s="4" t="inlineStr"/>
+      <c r="AC96" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
@@ -10825,7 +10865,11 @@
       <c r="AB98" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC98" s="4" t="inlineStr"/>
+      <c r="AC98" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
@@ -12356,7 +12400,11 @@
       <c r="AB113" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC113" s="4" t="inlineStr"/>
+      <c r="AC113" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="4" t="inlineStr">

--- a/docs/d/89/inyear.xlsx
+++ b/docs/d/89/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:41 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (99 days) - 4 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 4 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 33 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 28 clubs short</t>
         </is>
       </c>
     </row>
@@ -2605,7 +2605,7 @@
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" s="6" t="n">
         <v>10</v>
@@ -2675,8 +2675,8 @@
       <c r="Y19" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z19" s="9" t="n">
-        <v>0</v>
+      <c r="Z19" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA19" s="10" t="n">
         <v>1</v>
@@ -5806,7 +5806,7 @@
         </is>
       </c>
       <c r="E50" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F50" s="6" t="n">
         <v>10</v>
@@ -5876,8 +5876,8 @@
       <c r="Y50" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z50" s="9" t="n">
-        <v>0</v>
+      <c r="Z50" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA50" s="10" t="n">
         <v>1</v>
@@ -7274,13 +7274,13 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>40</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L64" s="4" t="inlineStr">
         <is>
@@ -7319,7 +7319,7 @@
         <v>0</v>
       </c>
       <c r="V64" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W64" s="9" t="n">
         <v>0</v>
@@ -7470,7 +7470,7 @@
         </is>
       </c>
       <c r="E66" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F66" s="6" t="n">
         <v>10</v>
@@ -7540,8 +7540,8 @@
       <c r="Y66" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z66" s="9" t="n">
-        <v>0</v>
+      <c r="Z66" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA66" s="10" t="n">
         <v>1</v>
@@ -8080,7 +8080,7 @@
         </is>
       </c>
       <c r="E72" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F72" s="6" t="n">
         <v>10</v>
@@ -8150,8 +8150,8 @@
       <c r="Y72" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z72" s="9" t="n">
-        <v>0</v>
+      <c r="Z72" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA72" s="10" t="n">
         <v>1</v>
@@ -10426,7 +10426,7 @@
         <v>1</v>
       </c>
       <c r="U94" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V94" s="9" t="n">
         <v>1</v>
@@ -11917,7 +11917,7 @@
         </is>
       </c>
       <c r="E109" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F109" s="6" t="n">
         <v>10</v>
@@ -11987,8 +11987,8 @@
       <c r="Y109" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z109" s="9" t="n">
-        <v>0</v>
+      <c r="Z109" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA109" s="10" t="n">
         <v>1</v>
@@ -13135,7 +13135,7 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -13366,7 +13366,7 @@
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -13498,7 +13498,7 @@
         <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -13531,7 +13531,7 @@
         <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -13828,7 +13828,7 @@
         <v>4</v>
       </c>
       <c r="D27" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>

--- a/docs/d/89/inyear.xlsx
+++ b/docs/d/89/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:41 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:23 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>276 days remain until 30 June 2027, when these scores become final.</t>
+          <t>269 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 4 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 4 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 28 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 13 clubs short</t>
         </is>
       </c>
     </row>
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="P2" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" s="9" t="n">
         <v>0</v>
@@ -918,8 +918,8 @@
       <c r="Y2" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z2" s="9" t="n">
-        <v>0</v>
+      <c r="Z2" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA2" s="9" t="n">
         <v>0</v>
@@ -2084,7 +2084,7 @@
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" s="6" t="n">
         <v>10</v>
@@ -2154,8 +2154,8 @@
       <c r="Y14" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z14" s="9" t="n">
-        <v>0</v>
+      <c r="Z14" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA14" s="10" t="n">
         <v>1</v>
@@ -2706,7 +2706,7 @@
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" s="6" t="n">
         <v>10</v>
@@ -2776,8 +2776,8 @@
       <c r="Y20" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z20" s="9" t="n">
-        <v>0</v>
+      <c r="Z20" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA20" s="10" t="n">
         <v>1</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F21" s="6" t="n">
         <v>10</v>
@@ -2877,8 +2877,8 @@
       <c r="Y21" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z21" s="9" t="n">
-        <v>0</v>
+      <c r="Z21" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA21" s="10" t="n">
         <v>1</v>
@@ -3841,7 +3841,7 @@
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F31" s="6" t="n">
         <v>10</v>
@@ -3911,8 +3911,8 @@
       <c r="Y31" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z31" s="9" t="n">
-        <v>0</v>
+      <c r="Z31" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA31" s="10" t="n">
         <v>1</v>
@@ -4707,7 +4707,7 @@
         <v>3</v>
       </c>
       <c r="Q39" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R39" s="9" t="n">
         <v>0</v>
@@ -5194,13 +5194,13 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
@@ -5239,7 +5239,7 @@
         <v>0</v>
       </c>
       <c r="V44" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W44" s="9" t="n">
         <v>0</v>
@@ -5326,7 +5326,7 @@
         </is>
       </c>
       <c r="P45" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q45" s="9" t="n">
         <v>0</v>
@@ -6121,7 +6121,7 @@
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F53" s="6" t="n">
         <v>10</v>
@@ -6191,8 +6191,8 @@
       <c r="Y53" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z53" s="9" t="n">
-        <v>0</v>
+      <c r="Z53" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA53" s="10" t="n">
         <v>1</v>
@@ -7892,13 +7892,13 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J70" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L70" s="7" t="inlineStr">
         <is>
@@ -7937,7 +7937,7 @@
         <v>0</v>
       </c>
       <c r="V70" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W70" s="9" t="n">
         <v>0</v>
@@ -7979,7 +7979,7 @@
         </is>
       </c>
       <c r="E71" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F71" s="6" t="n">
         <v>10</v>
@@ -8049,8 +8049,8 @@
       <c r="Y71" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z71" s="9" t="n">
-        <v>0</v>
+      <c r="Z71" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA71" s="10" t="n">
         <v>1</v>
@@ -8496,7 +8496,7 @@
         </is>
       </c>
       <c r="E76" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F76" s="6" t="n">
         <v>10</v>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="P76" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q76" s="9" t="n">
         <v>0</v>
@@ -8545,11 +8545,11 @@
       <c r="R76" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S76" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T76" s="9" t="n">
-        <v>0</v>
+      <c r="S76" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T76" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U76" s="9" t="n">
         <v>0</v>
@@ -8702,7 +8702,7 @@
         </is>
       </c>
       <c r="E78" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F78" s="6" t="n">
         <v>10</v>
@@ -8772,8 +8772,8 @@
       <c r="Y78" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z78" s="9" t="n">
-        <v>0</v>
+      <c r="Z78" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA78" s="10" t="n">
         <v>1</v>
@@ -9223,7 +9223,7 @@
         </is>
       </c>
       <c r="E83" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F83" s="6" t="n">
         <v>10</v>
@@ -9293,8 +9293,8 @@
       <c r="Y83" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z83" s="9" t="n">
-        <v>0</v>
+      <c r="Z83" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA83" s="10" t="n">
         <v>1</v>
@@ -9845,7 +9845,7 @@
         </is>
       </c>
       <c r="E89" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F89" s="6" t="n">
         <v>10</v>
@@ -9915,8 +9915,8 @@
       <c r="Y89" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z89" s="9" t="n">
-        <v>0</v>
+      <c r="Z89" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA89" s="10" t="n">
         <v>1</v>
@@ -10055,7 +10055,7 @@
         </is>
       </c>
       <c r="E91" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F91" s="6" t="n">
         <v>10</v>
@@ -10095,8 +10095,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P91" s="9" t="n">
-        <v>2</v>
+      <c r="P91" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q91" s="9" t="n">
         <v>0</v>
@@ -10265,7 +10265,7 @@
         </is>
       </c>
       <c r="E93" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F93" s="6" t="n">
         <v>10</v>
@@ -10335,8 +10335,8 @@
       <c r="Y93" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z93" s="9" t="n">
-        <v>0</v>
+      <c r="Z93" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA93" s="10" t="n">
         <v>1</v>
@@ -10891,7 +10891,7 @@
         </is>
       </c>
       <c r="E99" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F99" s="6" t="n">
         <v>10</v>
@@ -10961,8 +10961,8 @@
       <c r="Y99" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z99" s="9" t="n">
-        <v>0</v>
+      <c r="Z99" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA99" s="10" t="n">
         <v>1</v>
@@ -11404,7 +11404,7 @@
         </is>
       </c>
       <c r="E104" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F104" s="6" t="n">
         <v>10</v>
@@ -11474,8 +11474,8 @@
       <c r="Y104" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z104" s="9" t="n">
-        <v>0</v>
+      <c r="Z104" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA104" s="10" t="n">
         <v>1</v>
@@ -11816,7 +11816,7 @@
         </is>
       </c>
       <c r="E108" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F108" s="6" t="n">
         <v>10</v>
@@ -11886,8 +11886,8 @@
       <c r="Y108" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z108" s="9" t="n">
-        <v>0</v>
+      <c r="Z108" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA108" s="10" t="n">
         <v>1</v>
@@ -12335,13 +12335,13 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J113" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L113" s="4" t="inlineStr">
         <is>
@@ -12362,7 +12362,7 @@
         </is>
       </c>
       <c r="P113" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q113" s="9" t="n">
         <v>0</v>
@@ -12380,7 +12380,7 @@
         <v>0</v>
       </c>
       <c r="V113" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W113" s="9" t="n">
         <v>0</v>
@@ -12628,7 +12628,7 @@
         </is>
       </c>
       <c r="E116" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F116" s="6" t="n">
         <v>10</v>
@@ -12698,8 +12698,8 @@
       <c r="Y116" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z116" s="9" t="n">
-        <v>0</v>
+      <c r="Z116" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA116" s="10" t="n">
         <v>1</v>
@@ -13102,7 +13102,7 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -13135,7 +13135,7 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -13234,7 +13234,7 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -13399,7 +13399,7 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -13531,7 +13531,7 @@
         <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -13564,7 +13564,7 @@
         <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -13597,7 +13597,7 @@
         <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -13630,7 +13630,7 @@
         <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -13696,7 +13696,7 @@
         <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -13729,7 +13729,7 @@
         <v>4</v>
       </c>
       <c r="D24" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -13762,7 +13762,7 @@
         <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -13795,7 +13795,7 @@
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -13828,7 +13828,7 @@
         <v>4</v>
       </c>
       <c r="D27" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -13894,7 +13894,7 @@
         <v>5</v>
       </c>
       <c r="D29" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>

--- a/docs/d/89/inyear.xlsx
+++ b/docs/d/89/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:23 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>269 days remain until 30 June 2027, when these scores become final.</t>
+          <t>262 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 4 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 4 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 13 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 13 clubs short</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
         <v>0</v>
       </c>
       <c r="V2" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W2" s="9" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="E3" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" s="6" t="n">
         <v>10</v>
@@ -963,13 +963,13 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
@@ -1004,8 +1004,8 @@
       <c r="T3" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U3" s="9" t="n">
-        <v>0</v>
+      <c r="U3" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V3" s="9" t="n">
         <v>0</v>
@@ -1068,17 +1068,17 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L4" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M4" s="8" t="n">
@@ -1169,13 +1169,13 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
@@ -1274,13 +1274,13 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L6" s="7" t="inlineStr">
         <is>
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
@@ -1480,13 +1480,13 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>68</v>
+        <v>35</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>58</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>10</v>
+        <v>-23</v>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>4</v>
       </c>
       <c r="W8" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X8" s="10" t="n">
         <v>6</v>
@@ -1787,13 +1787,13 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F12" s="6" t="n">
         <v>10</v>
@@ -1892,13 +1892,13 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>49</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         </is>
       </c>
       <c r="P12" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q12" s="9" t="n">
         <v>0</v>
@@ -1936,11 +1936,11 @@
       <c r="U12" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V12" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" s="9" t="n">
-        <v>0</v>
+      <c r="V12" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W12" s="10" t="n">
+        <v>18</v>
       </c>
       <c r="X12" s="10" t="n">
         <v>4</v>
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F14" s="6" t="n">
         <v>10</v>
@@ -2098,13 +2098,13 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
@@ -2142,11 +2142,11 @@
       <c r="U14" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V14" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" s="9" t="n">
-        <v>0</v>
+      <c r="V14" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W14" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="X14" s="9" t="n">
         <v>0</v>
@@ -2189,7 +2189,7 @@
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F15" s="6" t="n">
         <v>10</v>
@@ -2203,13 +2203,13 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
@@ -2247,8 +2247,8 @@
       <c r="U15" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V15" s="9" t="n">
-        <v>3</v>
+      <c r="V15" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W15" s="9" t="n">
         <v>0</v>
@@ -2308,13 +2308,13 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
@@ -2413,13 +2413,13 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
@@ -2500,7 +2500,7 @@
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F18" s="6" t="n">
         <v>10</v>
@@ -2514,17 +2514,17 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L18" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M18" s="8" t="n">
@@ -2558,8 +2558,8 @@
       <c r="U18" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V18" s="9" t="n">
-        <v>1</v>
+      <c r="V18" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W18" s="9" t="n">
         <v>0</v>
@@ -2605,7 +2605,7 @@
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F19" s="6" t="n">
         <v>10</v>
@@ -2619,13 +2619,13 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
@@ -2663,8 +2663,8 @@
       <c r="U19" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V19" s="9" t="n">
-        <v>0</v>
+      <c r="V19" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W19" s="9" t="n">
         <v>0</v>
@@ -2720,13 +2720,13 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="L20" s="7" t="inlineStr">
         <is>
@@ -2821,13 +2821,13 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
@@ -2866,7 +2866,7 @@
         <v>0</v>
       </c>
       <c r="V21" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W21" s="9" t="n">
         <v>0</v>
@@ -3017,7 +3017,7 @@
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F23" s="6" t="n">
         <v>10</v>
@@ -3031,13 +3031,13 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>43</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
@@ -3075,11 +3075,11 @@
       <c r="U23" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V23" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W23" s="9" t="n">
-        <v>0</v>
+      <c r="V23" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W23" s="10" t="n">
+        <v>12</v>
       </c>
       <c r="X23" s="10" t="n">
         <v>4</v>
@@ -3136,13 +3136,13 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L24" s="7" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F25" s="6" t="n">
         <v>10</v>
@@ -3237,13 +3237,13 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L25" s="7" t="inlineStr">
         <is>
@@ -3281,8 +3281,8 @@
       <c r="U25" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V25" s="9" t="n">
-        <v>0</v>
+      <c r="V25" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W25" s="9" t="n">
         <v>0</v>
@@ -3338,13 +3338,13 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>38</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>2</v>
+        <v>-7</v>
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>0</v>
       </c>
       <c r="V26" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W26" s="9" t="n">
         <v>0</v>
@@ -3443,17 +3443,17 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L27" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M27" s="8" t="n">
@@ -3488,7 +3488,7 @@
         <v>0</v>
       </c>
       <c r="V27" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W27" s="9" t="n">
         <v>0</v>
@@ -3548,13 +3548,13 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L28" s="7" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         <v>0</v>
       </c>
       <c r="V28" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W28" s="9" t="n">
         <v>0</v>
@@ -3635,7 +3635,7 @@
         </is>
       </c>
       <c r="E29" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F29" s="6" t="n">
         <v>10</v>
@@ -3649,13 +3649,13 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
@@ -3693,8 +3693,8 @@
       <c r="U29" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V29" s="9" t="n">
-        <v>0</v>
+      <c r="V29" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W29" s="9" t="n">
         <v>0</v>
@@ -3750,13 +3750,13 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>45</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
         <v>4</v>
       </c>
       <c r="W30" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X30" s="10" t="n">
         <v>5</v>
@@ -3855,13 +3855,13 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
@@ -3900,7 +3900,7 @@
         <v>0</v>
       </c>
       <c r="V31" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W31" s="9" t="n">
         <v>0</v>
@@ -3956,13 +3956,13 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L32" s="7" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F34" s="6" t="n">
         <v>10</v>
@@ -4162,17 +4162,17 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L34" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M34" s="8" t="n">
@@ -4200,14 +4200,14 @@
       <c r="S34" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T34" s="9" t="n">
-        <v>0</v>
+      <c r="T34" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U34" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V34" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W34" s="9" t="n">
         <v>0</v>
@@ -4267,13 +4267,13 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
@@ -4368,17 +4368,17 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>41</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-41</v>
+      </c>
+      <c r="L36" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M36" s="8" t="n">
@@ -4473,17 +4473,17 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-12</v>
+      </c>
+      <c r="L37" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M37" s="8" t="n">
@@ -4500,10 +4500,10 @@
         </is>
       </c>
       <c r="P37" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q37" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R37" s="9" t="n">
         <v>0</v>
@@ -4564,7 +4564,7 @@
         </is>
       </c>
       <c r="E38" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F38" s="6" t="n">
         <v>10</v>
@@ -4578,17 +4578,17 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>-3</v>
-      </c>
-      <c r="L38" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>1</v>
+      </c>
+      <c r="L38" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M38" s="8" t="n">
@@ -4616,14 +4616,14 @@
       <c r="S38" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T38" s="9" t="n">
-        <v>0</v>
+      <c r="T38" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U38" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V38" s="9" t="n">
-        <v>0</v>
+      <c r="V38" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W38" s="9" t="n">
         <v>0</v>
@@ -4677,17 +4677,17 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L39" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L39" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M39" s="8" t="n">
@@ -4782,13 +4782,13 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>0</v>
       </c>
       <c r="V40" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W40" s="9" t="n">
         <v>0</v>
@@ -4883,17 +4883,17 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L41" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L41" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M41" s="8" t="n">
@@ -4988,13 +4988,13 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>1</v>
+        <v>-11</v>
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
@@ -5033,7 +5033,7 @@
         <v>0</v>
       </c>
       <c r="V42" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W42" s="9" t="n">
         <v>0</v>
@@ -5079,7 +5079,7 @@
         </is>
       </c>
       <c r="E43" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F43" s="6" t="n">
         <v>10</v>
@@ -5093,17 +5093,17 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>14</v>
+      </c>
+      <c r="L43" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M43" s="8" t="n">
@@ -5137,11 +5137,11 @@
       <c r="U43" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V43" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W43" s="9" t="n">
-        <v>0</v>
+      <c r="V43" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W43" s="10" t="n">
+        <v>10</v>
       </c>
       <c r="X43" s="9" t="n">
         <v>0</v>
@@ -5180,7 +5180,7 @@
         </is>
       </c>
       <c r="E44" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F44" s="6" t="n">
         <v>10</v>
@@ -5194,17 +5194,17 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L44" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L44" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M44" s="8" t="n">
@@ -5238,8 +5238,8 @@
       <c r="U44" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V44" s="9" t="n">
-        <v>3</v>
+      <c r="V44" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W44" s="9" t="n">
         <v>0</v>
@@ -5285,7 +5285,7 @@
         </is>
       </c>
       <c r="E45" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F45" s="6" t="n">
         <v>10</v>
@@ -5299,13 +5299,13 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>69</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
@@ -5346,8 +5346,8 @@
       <c r="V45" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W45" s="9" t="n">
-        <v>2</v>
+      <c r="W45" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X45" s="10" t="n">
         <v>4</v>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="P46" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q46" s="9" t="n">
         <v>0</v>
@@ -5509,13 +5509,13 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L47" s="7" t="inlineStr">
         <is>
@@ -5614,13 +5614,13 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L48" s="7" t="inlineStr">
         <is>
@@ -5650,7 +5650,7 @@
         <v>0</v>
       </c>
       <c r="S48" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T48" s="10" t="n">
         <v>1</v>
@@ -5715,13 +5715,13 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
@@ -5742,7 +5742,7 @@
         </is>
       </c>
       <c r="P49" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q49" s="10" t="n">
         <v>2</v>
@@ -5820,17 +5820,17 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-19</v>
+      </c>
+      <c r="L50" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M50" s="8" t="n">
@@ -5925,17 +5925,17 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L51" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L51" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M51" s="8" t="n">
@@ -6030,17 +6030,17 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L52" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L52" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M52" s="8" t="n">
@@ -6121,7 +6121,7 @@
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F53" s="6" t="n">
         <v>10</v>
@@ -6179,11 +6179,11 @@
       <c r="U53" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V53" s="9" t="n">
-        <v>0</v>
+      <c r="V53" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W53" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X53" s="9" t="n">
         <v>1</v>
@@ -6236,13 +6236,13 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L54" s="7" t="inlineStr">
         <is>
@@ -6341,13 +6341,13 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L55" s="4" t="inlineStr">
         <is>
@@ -6432,7 +6432,7 @@
         </is>
       </c>
       <c r="E56" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F56" s="6" t="n">
         <v>10</v>
@@ -6446,13 +6446,13 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L56" s="4" t="inlineStr">
         <is>
@@ -6490,11 +6490,11 @@
       <c r="U56" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V56" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W56" s="9" t="n">
-        <v>0</v>
+      <c r="V56" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W56" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="X56" s="10" t="n">
         <v>4</v>
@@ -6537,7 +6537,7 @@
         </is>
       </c>
       <c r="E57" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F57" s="6" t="n">
         <v>10</v>
@@ -6551,17 +6551,17 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L57" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L57" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M57" s="8" t="n">
@@ -6595,11 +6595,11 @@
       <c r="U57" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V57" s="9" t="n">
-        <v>1</v>
+      <c r="V57" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W57" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X57" s="10" t="n">
         <v>6</v>
@@ -6642,7 +6642,7 @@
         </is>
       </c>
       <c r="E58" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F58" s="6" t="n">
         <v>10</v>
@@ -6656,13 +6656,13 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J58" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L58" s="4" t="inlineStr">
         <is>
@@ -6703,8 +6703,8 @@
       <c r="V58" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W58" s="9" t="n">
-        <v>3</v>
+      <c r="W58" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X58" s="10" t="n">
         <v>4</v>
@@ -6866,17 +6866,17 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L60" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L60" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M60" s="8" t="n">
@@ -6971,17 +6971,17 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L61" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L61" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M61" s="8" t="n">
@@ -7274,13 +7274,13 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>40</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L64" s="4" t="inlineStr">
         <is>
@@ -7319,7 +7319,7 @@
         <v>0</v>
       </c>
       <c r="V64" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W64" s="9" t="n">
         <v>0</v>
@@ -7379,13 +7379,13 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J65" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
@@ -7529,7 +7529,7 @@
         <v>0</v>
       </c>
       <c r="V66" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W66" s="9" t="n">
         <v>0</v>
@@ -7686,13 +7686,13 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L68" s="4" t="inlineStr">
         <is>
@@ -7731,7 +7731,7 @@
         <v>0</v>
       </c>
       <c r="V68" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W68" s="9" t="n">
         <v>0</v>
@@ -7787,17 +7787,17 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L69" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L69" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M69" s="8" t="n">
@@ -7832,7 +7832,7 @@
         <v>0</v>
       </c>
       <c r="V69" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W69" s="9" t="n">
         <v>0</v>
@@ -7892,13 +7892,13 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J70" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L70" s="7" t="inlineStr">
         <is>
@@ -8094,13 +8094,13 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J72" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="L72" s="7" t="inlineStr">
         <is>
@@ -8199,17 +8199,17 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L73" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L73" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M73" s="8" t="n">
@@ -8304,13 +8304,13 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L74" s="7" t="inlineStr">
         <is>
@@ -8405,17 +8405,17 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L75" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-19</v>
+      </c>
+      <c r="L75" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M75" s="8" t="n">
@@ -8496,7 +8496,7 @@
         </is>
       </c>
       <c r="E76" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F76" s="6" t="n">
         <v>10</v>
@@ -8510,13 +8510,13 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>39</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>1</v>
+        <v>-7</v>
       </c>
       <c r="L76" s="4" t="inlineStr">
         <is>
@@ -8554,8 +8554,8 @@
       <c r="U76" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V76" s="9" t="n">
-        <v>1</v>
+      <c r="V76" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W76" s="9" t="n">
         <v>0</v>
@@ -8615,13 +8615,13 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L77" s="7" t="inlineStr">
         <is>
@@ -8716,13 +8716,13 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>1</v>
+        <v>-7</v>
       </c>
       <c r="L78" s="7" t="inlineStr">
         <is>
@@ -8803,7 +8803,7 @@
         </is>
       </c>
       <c r="E79" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F79" s="6" t="n">
         <v>10</v>
@@ -8817,17 +8817,17 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L79" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L79" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M79" s="8" t="n">
@@ -8861,8 +8861,8 @@
       <c r="U79" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V79" s="9" t="n">
-        <v>3</v>
+      <c r="V79" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W79" s="9" t="n">
         <v>0</v>
@@ -8922,17 +8922,17 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L80" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L80" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M80" s="8" t="n">
@@ -8967,7 +8967,7 @@
         <v>0</v>
       </c>
       <c r="V80" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W80" s="9" t="n">
         <v>0</v>
@@ -9027,17 +9027,17 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J81" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L81" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L81" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M81" s="8" t="n">
@@ -9132,17 +9132,17 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L82" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L82" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M82" s="8" t="n">
@@ -9338,13 +9338,13 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>6</v>
+        <v>-5</v>
       </c>
       <c r="L84" s="4" t="inlineStr">
         <is>
@@ -9386,7 +9386,7 @@
         <v>4</v>
       </c>
       <c r="W84" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X84" s="10" t="n">
         <v>4</v>
@@ -9429,7 +9429,7 @@
         </is>
       </c>
       <c r="E85" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F85" s="6" t="n">
         <v>10</v>
@@ -9443,13 +9443,13 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
       <c r="L85" s="4" t="inlineStr">
         <is>
@@ -9487,8 +9487,8 @@
       <c r="U85" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V85" s="9" t="n">
-        <v>3</v>
+      <c r="V85" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W85" s="9" t="n">
         <v>0</v>
@@ -9548,13 +9548,13 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L86" s="7" t="inlineStr">
         <is>
@@ -9649,13 +9649,13 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="J87" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L87" s="7" t="inlineStr">
         <is>
@@ -9754,13 +9754,13 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L88" s="4" t="inlineStr">
         <is>
@@ -9799,7 +9799,7 @@
         <v>0</v>
       </c>
       <c r="V88" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W88" s="9" t="n">
         <v>0</v>
@@ -9859,17 +9859,17 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L89" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L89" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M89" s="8" t="n">
@@ -9904,7 +9904,7 @@
         <v>0</v>
       </c>
       <c r="V89" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W89" s="9" t="n">
         <v>0</v>
@@ -9964,13 +9964,13 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>4</v>
+        <v>-3</v>
       </c>
       <c r="L90" s="4" t="inlineStr">
         <is>
@@ -10012,7 +10012,7 @@
         <v>4</v>
       </c>
       <c r="W90" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X90" s="10" t="n">
         <v>7</v>
@@ -10069,13 +10069,13 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L91" s="7" t="inlineStr">
         <is>
@@ -10174,17 +10174,17 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J92" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L92" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L92" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M92" s="8" t="n">
@@ -10219,7 +10219,7 @@
         <v>0</v>
       </c>
       <c r="V92" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W92" s="9" t="n">
         <v>0</v>
@@ -10279,17 +10279,17 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L93" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-12</v>
+      </c>
+      <c r="L93" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M93" s="8" t="n">
@@ -10384,17 +10384,17 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L94" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L94" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M94" s="8" t="n">
@@ -10411,7 +10411,7 @@
         </is>
       </c>
       <c r="P94" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q94" s="9" t="n">
         <v>0</v>
@@ -10576,7 +10576,7 @@
         </is>
       </c>
       <c r="E96" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F96" s="6" t="n">
         <v>10</v>
@@ -10590,13 +10590,13 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L96" s="4" t="inlineStr">
         <is>
@@ -10634,8 +10634,8 @@
       <c r="U96" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V96" s="9" t="n">
-        <v>0</v>
+      <c r="V96" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W96" s="9" t="n">
         <v>0</v>
@@ -10695,17 +10695,17 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L97" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-15</v>
+      </c>
+      <c r="L97" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M97" s="8" t="n">
@@ -10740,7 +10740,7 @@
         <v>0</v>
       </c>
       <c r="V97" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W97" s="9" t="n">
         <v>0</v>
@@ -10800,13 +10800,13 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="J98" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L98" s="4" t="inlineStr">
         <is>
@@ -10848,7 +10848,7 @@
         <v>4</v>
       </c>
       <c r="W98" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X98" s="10" t="n">
         <v>6</v>
@@ -10891,7 +10891,7 @@
         </is>
       </c>
       <c r="E99" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F99" s="6" t="n">
         <v>10</v>
@@ -10905,13 +10905,13 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L99" s="7" t="inlineStr">
         <is>
@@ -10943,14 +10943,14 @@
       <c r="S99" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T99" s="9" t="n">
-        <v>0</v>
+      <c r="T99" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U99" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V99" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W99" s="9" t="n">
         <v>0</v>
@@ -11006,13 +11006,13 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L100" s="7" t="inlineStr">
         <is>
@@ -11107,13 +11107,13 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L101" s="4" t="inlineStr">
         <is>
@@ -11212,17 +11212,17 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L102" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L102" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M102" s="8" t="n">
@@ -11257,7 +11257,7 @@
         <v>0</v>
       </c>
       <c r="V102" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W102" s="9" t="n">
         <v>0</v>
@@ -11317,13 +11317,13 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J103" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L103" s="7" t="inlineStr">
         <is>
@@ -11418,13 +11418,13 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J104" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L104" s="7" t="inlineStr">
         <is>
@@ -11463,7 +11463,7 @@
         <v>0</v>
       </c>
       <c r="V104" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W104" s="9" t="n">
         <v>0</v>
@@ -11620,13 +11620,13 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L106" s="7" t="inlineStr">
         <is>
@@ -11665,7 +11665,7 @@
         <v>0</v>
       </c>
       <c r="V106" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W106" s="9" t="n">
         <v>0</v>
@@ -11725,17 +11725,17 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="J107" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L107" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-15</v>
+      </c>
+      <c r="L107" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M107" s="8" t="n">
@@ -11816,7 +11816,7 @@
         </is>
       </c>
       <c r="E108" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F108" s="6" t="n">
         <v>10</v>
@@ -11830,13 +11830,13 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L108" s="7" t="inlineStr">
         <is>
@@ -11874,8 +11874,8 @@
       <c r="U108" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V108" s="9" t="n">
-        <v>1</v>
+      <c r="V108" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W108" s="9" t="n">
         <v>0</v>
@@ -11931,13 +11931,13 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L109" s="4" t="inlineStr">
         <is>
@@ -12032,17 +12032,17 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L110" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-12</v>
+      </c>
+      <c r="L110" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M110" s="8" t="n">
@@ -12133,13 +12133,13 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L111" s="7" t="inlineStr">
         <is>
@@ -12321,7 +12321,7 @@
         </is>
       </c>
       <c r="E113" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F113" s="6" t="n">
         <v>10</v>
@@ -12335,13 +12335,13 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="J113" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
       <c r="L113" s="4" t="inlineStr">
         <is>
@@ -12379,8 +12379,8 @@
       <c r="U113" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V113" s="9" t="n">
-        <v>3</v>
+      <c r="V113" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W113" s="9" t="n">
         <v>0</v>
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J114" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L114" s="7" t="inlineStr">
         <is>
@@ -12541,13 +12541,13 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J115" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L115" s="7" t="inlineStr">
         <is>
@@ -12586,7 +12586,7 @@
         <v>0</v>
       </c>
       <c r="V115" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W115" s="9" t="n">
         <v>0</v>
@@ -12642,13 +12642,13 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J116" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L116" s="7" t="inlineStr">
         <is>
@@ -12687,7 +12687,7 @@
         <v>0</v>
       </c>
       <c r="V116" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W116" s="9" t="n">
         <v>0</v>
@@ -12743,13 +12743,13 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="J117" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L117" s="4" t="inlineStr">
         <is>
@@ -12788,7 +12788,7 @@
         <v>0</v>
       </c>
       <c r="V117" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W117" s="9" t="n">
         <v>0</v>
@@ -12834,7 +12834,7 @@
         </is>
       </c>
       <c r="E118" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F118" s="6" t="n">
         <v>10</v>
@@ -12848,13 +12848,13 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J118" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L118" s="7" t="inlineStr">
         <is>
@@ -12892,8 +12892,8 @@
       <c r="U118" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V118" s="9" t="n">
-        <v>0</v>
+      <c r="V118" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W118" s="9" t="n">
         <v>0</v>
@@ -13003,7 +13003,7 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -13018,7 +13018,7 @@
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -13069,13 +13069,13 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -13102,7 +13102,7 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -13135,7 +13135,7 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -13150,7 +13150,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -13168,7 +13168,7 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -13201,7 +13201,7 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -13216,7 +13216,7 @@
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -13267,7 +13267,7 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -13282,7 +13282,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -13300,7 +13300,7 @@
         <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>1.17</v>
+        <v>1.83</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -13333,7 +13333,7 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
@@ -13348,7 +13348,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -13381,7 +13381,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -13399,7 +13399,7 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -13414,7 +13414,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -13432,7 +13432,7 @@
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -13447,7 +13447,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -13480,7 +13480,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -13546,7 +13546,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -13564,7 +13564,7 @@
         <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -13579,7 +13579,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -13597,7 +13597,7 @@
         <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -13612,7 +13612,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -13645,7 +13645,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -13663,7 +13663,7 @@
         <v>4</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -13711,7 +13711,7 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -13729,7 +13729,7 @@
         <v>4</v>
       </c>
       <c r="D24" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -13744,7 +13744,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -13762,7 +13762,7 @@
         <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -13777,7 +13777,7 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -13810,7 +13810,7 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -13828,7 +13828,7 @@
         <v>4</v>
       </c>
       <c r="D27" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -13843,7 +13843,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -13861,7 +13861,7 @@
         <v>4</v>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -13876,7 +13876,7 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -13894,7 +13894,7 @@
         <v>5</v>
       </c>
       <c r="D29" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>

--- a/docs/d/89/inyear.xlsx
+++ b/docs/d/89/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/89/inyear.xlsx
+++ b/docs/d/89/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:57 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/89/inyear.xlsx
+++ b/docs/d/89/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:57 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/89/inyear.xlsx
+++ b/docs/d/89/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/89/inyear.xlsx
+++ b/docs/d/89/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 4 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 4 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 13 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 13 clubs short</t>
         </is>
       </c>
     </row>
@@ -963,13 +963,13 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
@@ -1005,10 +1005,10 @@
         <v>1</v>
       </c>
       <c r="U3" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V3" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W3" s="9" t="n">
         <v>0</v>
@@ -1205,7 +1205,7 @@
         <v>0</v>
       </c>
       <c r="S5" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T5" s="9" t="n">
         <v>0</v>
@@ -1466,7 +1466,7 @@
         </is>
       </c>
       <c r="E8" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>10</v>
@@ -1480,13 +1480,13 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>58</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-23</v>
+        <v>-24</v>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         </is>
       </c>
       <c r="P8" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q8" s="9" t="n">
         <v>1</v>
@@ -1515,8 +1515,8 @@
       <c r="R8" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S8" s="9" t="n">
-        <v>1</v>
+      <c r="S8" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T8" s="9" t="n">
         <v>0</v>
@@ -1528,7 +1528,7 @@
         <v>4</v>
       </c>
       <c r="W8" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X8" s="10" t="n">
         <v>6</v>
@@ -1919,7 +1919,7 @@
         </is>
       </c>
       <c r="P12" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q12" s="9" t="n">
         <v>0</v>
@@ -3237,13 +3237,13 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L25" s="7" t="inlineStr">
         <is>
@@ -3285,7 +3285,7 @@
         <v>4</v>
       </c>
       <c r="W25" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X25" s="9" t="n">
         <v>1</v>
@@ -4084,7 +4084,7 @@
         </is>
       </c>
       <c r="P33" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q33" s="10" t="n">
         <v>2</v>
@@ -4473,13 +4473,13 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>-12</v>
+        <v>-10</v>
       </c>
       <c r="L37" s="7" t="inlineStr">
         <is>
@@ -4869,7 +4869,7 @@
         </is>
       </c>
       <c r="E41" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F41" s="6" t="n">
         <v>10</v>
@@ -4921,8 +4921,8 @@
       <c r="S41" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T41" s="9" t="n">
-        <v>0</v>
+      <c r="T41" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U41" s="9" t="n">
         <v>0</v>
@@ -5701,7 +5701,7 @@
         </is>
       </c>
       <c r="E49" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F49" s="6" t="n">
         <v>10</v>
@@ -5715,13 +5715,13 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
@@ -5759,8 +5759,8 @@
       <c r="U49" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V49" s="9" t="n">
-        <v>2</v>
+      <c r="V49" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W49" s="9" t="n">
         <v>0</v>
@@ -6446,13 +6446,13 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L56" s="4" t="inlineStr">
         <is>
@@ -6494,7 +6494,7 @@
         <v>4</v>
       </c>
       <c r="W56" s="10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X56" s="10" t="n">
         <v>4</v>
@@ -7072,13 +7072,13 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L62" s="7" t="inlineStr">
         <is>
@@ -7117,7 +7117,7 @@
         <v>0</v>
       </c>
       <c r="V62" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W62" s="9" t="n">
         <v>0</v>
@@ -9013,7 +9013,7 @@
         </is>
       </c>
       <c r="E81" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F81" s="6" t="n">
         <v>10</v>
@@ -9062,8 +9062,8 @@
       <c r="R81" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S81" s="9" t="n">
-        <v>1</v>
+      <c r="S81" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T81" s="9" t="n">
         <v>0</v>
@@ -9324,7 +9324,7 @@
         </is>
       </c>
       <c r="E84" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F84" s="6" t="n">
         <v>10</v>
@@ -9338,13 +9338,13 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L84" s="4" t="inlineStr">
         <is>
@@ -9385,8 +9385,8 @@
       <c r="V84" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W84" s="9" t="n">
-        <v>3</v>
+      <c r="W84" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X84" s="10" t="n">
         <v>4</v>
@@ -10695,13 +10695,13 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>-15</v>
+        <v>-14</v>
       </c>
       <c r="L97" s="7" t="inlineStr">
         <is>
@@ -10740,7 +10740,7 @@
         <v>0</v>
       </c>
       <c r="V97" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W97" s="9" t="n">
         <v>0</v>
@@ -11093,7 +11093,7 @@
         </is>
       </c>
       <c r="E101" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F101" s="6" t="n">
         <v>10</v>
@@ -11145,8 +11145,8 @@
       <c r="S101" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="T101" s="9" t="n">
-        <v>0</v>
+      <c r="T101" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U101" s="9" t="n">
         <v>0</v>
@@ -11212,13 +11212,13 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L102" s="7" t="inlineStr">
         <is>
@@ -11257,7 +11257,7 @@
         <v>0</v>
       </c>
       <c r="V102" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W102" s="9" t="n">
         <v>0</v>
@@ -12160,7 +12160,7 @@
         </is>
       </c>
       <c r="P111" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q111" s="9" t="n">
         <v>0</v>
@@ -12234,13 +12234,13 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J112" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L112" s="4" t="inlineStr">
         <is>
@@ -12279,7 +12279,7 @@
         <v>0</v>
       </c>
       <c r="V112" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W112" s="9" t="n">
         <v>0</v>
@@ -12335,13 +12335,13 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J113" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L113" s="4" t="inlineStr">
         <is>
@@ -13036,7 +13036,7 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -13300,7 +13300,7 @@
         <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -13366,13 +13366,13 @@
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -13630,7 +13630,7 @@
         <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -13795,7 +13795,7 @@
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>

--- a/docs/d/89/inyear.xlsx
+++ b/docs/d/89/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:50 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 4 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (67 days) - 4 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 13 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 13 clubs short</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="P3" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" s="9" t="n">
         <v>0</v>
@@ -1480,13 +1480,13 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>58</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-24</v>
+        <v>-23</v>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>4</v>
       </c>
       <c r="W8" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X8" s="10" t="n">
         <v>6</v>
@@ -2098,13 +2098,13 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>4</v>
       </c>
       <c r="W14" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X14" s="9" t="n">
         <v>0</v>
@@ -3067,7 +3067,7 @@
         <v>0</v>
       </c>
       <c r="S23" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T23" s="9" t="n">
         <v>0</v>
@@ -3237,13 +3237,13 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L25" s="7" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
         </is>
       </c>
       <c r="E26" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F26" s="6" t="n">
         <v>10</v>
@@ -3338,13 +3338,13 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>38</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
         <v>0</v>
       </c>
       <c r="Q26" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R26" s="9" t="n">
         <v>0</v>
@@ -3382,8 +3382,8 @@
       <c r="U26" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V26" s="9" t="n">
-        <v>3</v>
+      <c r="V26" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W26" s="9" t="n">
         <v>0</v>
@@ -4267,13 +4267,13 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
@@ -4473,13 +4473,13 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L37" s="7" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="E51" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F51" s="6" t="n">
         <v>10</v>
@@ -5966,8 +5966,8 @@
       <c r="T51" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U51" s="9" t="n">
-        <v>0</v>
+      <c r="U51" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="V51" s="9" t="n">
         <v>1</v>
@@ -6135,13 +6135,13 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="E60" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F60" s="6" t="n">
         <v>10</v>
@@ -6904,8 +6904,8 @@
       <c r="S60" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T60" s="9" t="n">
-        <v>0</v>
+      <c r="T60" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U60" s="9" t="n">
         <v>0</v>
@@ -9324,7 +9324,7 @@
         </is>
       </c>
       <c r="E84" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F84" s="6" t="n">
         <v>10</v>
@@ -9373,8 +9373,8 @@
       <c r="R84" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S84" s="9" t="n">
-        <v>1</v>
+      <c r="S84" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T84" s="10" t="n">
         <v>1</v>
@@ -9575,7 +9575,7 @@
         </is>
       </c>
       <c r="P86" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q86" s="9" t="n">
         <v>0</v>
@@ -9781,7 +9781,7 @@
         </is>
       </c>
       <c r="P88" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q88" s="9" t="n">
         <v>0</v>
@@ -9859,13 +9859,13 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="L89" s="7" t="inlineStr">
         <is>
@@ -10069,13 +10069,13 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L91" s="7" t="inlineStr">
         <is>
@@ -10114,7 +10114,7 @@
         <v>0</v>
       </c>
       <c r="V91" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W91" s="9" t="n">
         <v>0</v>
@@ -10681,7 +10681,7 @@
         </is>
       </c>
       <c r="E97" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F97" s="6" t="n">
         <v>10</v>
@@ -10695,13 +10695,13 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="L97" s="7" t="inlineStr">
         <is>
@@ -10731,16 +10731,16 @@
         <v>0</v>
       </c>
       <c r="S97" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T97" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T97" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U97" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V97" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W97" s="9" t="n">
         <v>0</v>
@@ -10891,7 +10891,7 @@
         </is>
       </c>
       <c r="E99" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F99" s="6" t="n">
         <v>10</v>
@@ -10905,13 +10905,13 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L99" s="7" t="inlineStr">
         <is>
@@ -10949,8 +10949,8 @@
       <c r="U99" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V99" s="9" t="n">
-        <v>3</v>
+      <c r="V99" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W99" s="9" t="n">
         <v>0</v>
@@ -13201,7 +13201,7 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -13366,7 +13366,7 @@
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
@@ -13465,7 +13465,7 @@
         <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -13630,13 +13630,13 @@
         <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -13762,7 +13762,7 @@
         <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
